--- a/Intersecciones/excels/PUNO-MELGAR-AYAVIRI.xlsx
+++ b/Intersecciones/excels/PUNO-MELGAR-AYAVIRI.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +948,110 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-198482</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>210806</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MELGAR</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NUÑOA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-14.6488634</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-70.6412311</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>210801</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-198824</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>210806</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MELGAR</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NUÑOA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-14.4434494</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-70.664887</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>210801</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
